--- a/evaluations.xlsx
+++ b/evaluations.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hhoar\IdeaProjects\OasisTools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A16F3B87-8446-459A-9EAE-FB3B591A23F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA4A0AC-90F8-4D97-936E-4BB795AB219B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="34776" windowHeight="18936" xr2:uid="{7A85ACFF-515C-4F42-BD6C-13C15AB38619}"/>
+    <workbookView xWindow="-28920" yWindow="11370" windowWidth="29040" windowHeight="15720" xr2:uid="{7A85ACFF-515C-4F42-BD6C-13C15AB38619}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="258">
   <si>
     <t>Discipline</t>
   </si>
@@ -49,13 +50,772 @@
   </si>
   <si>
     <t>Comment</t>
+  </si>
+  <si>
+    <t>VALIDATE</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>nokuda</t>
+  </si>
+  <si>
+    <t>garaujodealmeida</t>
+  </si>
+  <si>
+    <t>skawai</t>
+  </si>
+  <si>
+    <t>sshin</t>
+  </si>
+  <si>
+    <t>tsuzuki</t>
+  </si>
+  <si>
+    <t>acantonnet</t>
+  </si>
+  <si>
+    <t>clee</t>
+  </si>
+  <si>
+    <t>ldepoli</t>
+  </si>
+  <si>
+    <t>schauvire</t>
+  </si>
+  <si>
+    <t>wtechin</t>
+  </si>
+  <si>
+    <t>acesari</t>
+  </si>
+  <si>
+    <t>dtabacaru</t>
+  </si>
+  <si>
+    <t>egrandcolas</t>
+  </si>
+  <si>
+    <t>gfoisseau</t>
+  </si>
+  <si>
+    <t>jblemoine</t>
+  </si>
+  <si>
+    <t>jmialon</t>
+  </si>
+  <si>
+    <t>lboulat</t>
+  </si>
+  <si>
+    <t>pefaye</t>
+  </si>
+  <si>
+    <t>[[ CODE ]]</t>
+  </si>
+  <si>
+    <t>Identifiant Oasis</t>
+  </si>
+  <si>
+    <t>pfaget</t>
+  </si>
+  <si>
+    <t>ppradier</t>
+  </si>
+  <si>
+    <t>ytakasaki</t>
+  </si>
+  <si>
+    <t>aavezardabdelghafour</t>
+  </si>
+  <si>
+    <t>agautier</t>
+  </si>
+  <si>
+    <t>cfrancois</t>
+  </si>
+  <si>
+    <t>cmachicot</t>
+  </si>
+  <si>
+    <t>dheusler</t>
+  </si>
+  <si>
+    <t>econstable</t>
+  </si>
+  <si>
+    <t>gsardier</t>
+  </si>
+  <si>
+    <t>iwingborg</t>
+  </si>
+  <si>
+    <t>kujisawa</t>
+  </si>
+  <si>
+    <t>mgiraud1</t>
+  </si>
+  <si>
+    <t>msekfalibonnier</t>
+  </si>
+  <si>
+    <t>abomont</t>
+  </si>
+  <si>
+    <t>cfremau</t>
+  </si>
+  <si>
+    <t>hye</t>
+  </si>
+  <si>
+    <t>jfamchon</t>
+  </si>
+  <si>
+    <t>jhuang1</t>
+  </si>
+  <si>
+    <t>jpostel</t>
+  </si>
+  <si>
+    <t>lguilleux</t>
+  </si>
+  <si>
+    <t>lsardinameesemaecker</t>
+  </si>
+  <si>
+    <t>mlenormand</t>
+  </si>
+  <si>
+    <t>moudone</t>
+  </si>
+  <si>
+    <t>ofoulliaron</t>
+  </si>
+  <si>
+    <t>rdehors</t>
+  </si>
+  <si>
+    <t>rpogam</t>
+  </si>
+  <si>
+    <t>sdefromont</t>
+  </si>
+  <si>
+    <t>tdupuis</t>
+  </si>
+  <si>
+    <t>tpouye</t>
+  </si>
+  <si>
+    <t>agross1</t>
+  </si>
+  <si>
+    <t>ahuerta</t>
+  </si>
+  <si>
+    <t>amansart</t>
+  </si>
+  <si>
+    <t>asbornens</t>
+  </si>
+  <si>
+    <t>bnaji</t>
+  </si>
+  <si>
+    <t>crouge</t>
+  </si>
+  <si>
+    <t>ebertrand</t>
+  </si>
+  <si>
+    <t>edoumic</t>
+  </si>
+  <si>
+    <t>fmartin2</t>
+  </si>
+  <si>
+    <t>htaguchi</t>
+  </si>
+  <si>
+    <t>jmassard</t>
+  </si>
+  <si>
+    <t>khoskova</t>
+  </si>
+  <si>
+    <t>lbressoux</t>
+  </si>
+  <si>
+    <t>lrueda</t>
+  </si>
+  <si>
+    <t>mathanebest</t>
+  </si>
+  <si>
+    <t>mbiscuit</t>
+  </si>
+  <si>
+    <t>mmnatsakanyan</t>
+  </si>
+  <si>
+    <t>onguyen</t>
+  </si>
+  <si>
+    <t>plorthios</t>
+  </si>
+  <si>
+    <t>rlacombe</t>
+  </si>
+  <si>
+    <t>rnormand-condat</t>
+  </si>
+  <si>
+    <t>slim</t>
+  </si>
+  <si>
+    <t>smiceli</t>
+  </si>
+  <si>
+    <t>snobilet</t>
+  </si>
+  <si>
+    <t>ssroulette</t>
+  </si>
+  <si>
+    <t>syoon</t>
+  </si>
+  <si>
+    <t>taguerre</t>
+  </si>
+  <si>
+    <t>acarde</t>
+  </si>
+  <si>
+    <t>acaze</t>
+  </si>
+  <si>
+    <t>aesmaeilzadeh</t>
+  </si>
+  <si>
+    <t>athevenin</t>
+  </si>
+  <si>
+    <t>cmoreau1</t>
+  </si>
+  <si>
+    <t>ecaron</t>
+  </si>
+  <si>
+    <t>fdeschodt</t>
+  </si>
+  <si>
+    <t>gfabien</t>
+  </si>
+  <si>
+    <t>izajtmann1</t>
+  </si>
+  <si>
+    <t>jbbatoge</t>
+  </si>
+  <si>
+    <t>jszulcbaptista</t>
+  </si>
+  <si>
+    <t>mdicapua</t>
+  </si>
+  <si>
+    <t>mulrich</t>
+  </si>
+  <si>
+    <t>nlastere</t>
+  </si>
+  <si>
+    <t>plagondjondenguinot</t>
+  </si>
+  <si>
+    <t>skim4</t>
+  </si>
+  <si>
+    <t>sleretlemestre</t>
+  </si>
+  <si>
+    <t>vananthakkarasu</t>
+  </si>
+  <si>
+    <t>yamano</t>
+  </si>
+  <si>
+    <t>aberson</t>
+  </si>
+  <si>
+    <t>abich</t>
+  </si>
+  <si>
+    <t>agrizard</t>
+  </si>
+  <si>
+    <t>ajeannot</t>
+  </si>
+  <si>
+    <t>apesnel</t>
+  </si>
+  <si>
+    <t>cpauvert</t>
+  </si>
+  <si>
+    <t>dlau</t>
+  </si>
+  <si>
+    <t>emeens</t>
+  </si>
+  <si>
+    <t>hjoly</t>
+  </si>
+  <si>
+    <t>jcharles2</t>
+  </si>
+  <si>
+    <t>jferrer</t>
+  </si>
+  <si>
+    <t>jperez1</t>
+  </si>
+  <si>
+    <t>lbelon</t>
+  </si>
+  <si>
+    <t>mjyxu</t>
+  </si>
+  <si>
+    <t>mshiozawa</t>
+  </si>
+  <si>
+    <t>rmoeller</t>
+  </si>
+  <si>
+    <t>skalinowski</t>
+  </si>
+  <si>
+    <t>spark</t>
+  </si>
+  <si>
+    <t>tjen</t>
+  </si>
+  <si>
+    <t>tlemaire</t>
+  </si>
+  <si>
+    <t>vchauvet</t>
+  </si>
+  <si>
+    <t>vconesa</t>
+  </si>
+  <si>
+    <t>abobtcheff</t>
+  </si>
+  <si>
+    <t>akerouanton</t>
+  </si>
+  <si>
+    <t>gnguyen</t>
+  </si>
+  <si>
+    <t>jce</t>
+  </si>
+  <si>
+    <t>jpoumes</t>
+  </si>
+  <si>
+    <t>kespinasse</t>
+  </si>
+  <si>
+    <t>ladutreix</t>
+  </si>
+  <si>
+    <t>lleneman</t>
+  </si>
+  <si>
+    <t>lvgrillo</t>
+  </si>
+  <si>
+    <t>mblouet</t>
+  </si>
+  <si>
+    <t>mroumegas</t>
+  </si>
+  <si>
+    <t>mvignier</t>
+  </si>
+  <si>
+    <t>nemoscardo</t>
+  </si>
+  <si>
+    <t>njosselin</t>
+  </si>
+  <si>
+    <t>pfritz</t>
+  </si>
+  <si>
+    <t>pmuslewski</t>
+  </si>
+  <si>
+    <t>rkazandjian</t>
+  </si>
+  <si>
+    <t>rleblond</t>
+  </si>
+  <si>
+    <t>syagi</t>
+  </si>
+  <si>
+    <t>zgogris</t>
+  </si>
+  <si>
+    <t>abettencourt</t>
+  </si>
+  <si>
+    <t>achristophe1</t>
+  </si>
+  <si>
+    <t>acimbault</t>
+  </si>
+  <si>
+    <t>asostrupkristensen</t>
+  </si>
+  <si>
+    <t>ctallet1</t>
+  </si>
+  <si>
+    <t>dbondetdelabernardie</t>
+  </si>
+  <si>
+    <t>dchoisi</t>
+  </si>
+  <si>
+    <t>epaccou</t>
+  </si>
+  <si>
+    <t>ericard</t>
+  </si>
+  <si>
+    <t>erodrigues</t>
+  </si>
+  <si>
+    <t>esezestre</t>
+  </si>
+  <si>
+    <t>fprat</t>
+  </si>
+  <si>
+    <t>gwelcker</t>
+  </si>
+  <si>
+    <t>hsato</t>
+  </si>
+  <si>
+    <t>jdoursout</t>
+  </si>
+  <si>
+    <t>lmessina</t>
+  </si>
+  <si>
+    <t>lminghetti</t>
+  </si>
+  <si>
+    <t>mamellies</t>
+  </si>
+  <si>
+    <t>mmetzger</t>
+  </si>
+  <si>
+    <t>mmichel1</t>
+  </si>
+  <si>
+    <t>mseto</t>
+  </si>
+  <si>
+    <t>mshcherbina</t>
+  </si>
+  <si>
+    <t>mvalero</t>
+  </si>
+  <si>
+    <t>nduboille</t>
+  </si>
+  <si>
+    <t>nnoufel</t>
+  </si>
+  <si>
+    <t>nroyer</t>
+  </si>
+  <si>
+    <t>nsmangloma</t>
+  </si>
+  <si>
+    <t>pgermanaz</t>
+  </si>
+  <si>
+    <t>stheodas</t>
+  </si>
+  <si>
+    <t>tguilbertselb</t>
+  </si>
+  <si>
+    <t>twilson</t>
+  </si>
+  <si>
+    <t>vgadin</t>
+  </si>
+  <si>
+    <t>adelhoume</t>
+  </si>
+  <si>
+    <t>alvgalichet</t>
+  </si>
+  <si>
+    <t>amoen</t>
+  </si>
+  <si>
+    <t>cbrunet</t>
+  </si>
+  <si>
+    <t>ccoppola</t>
+  </si>
+  <si>
+    <t>cmellardi</t>
+  </si>
+  <si>
+    <t>cmessina</t>
+  </si>
+  <si>
+    <t>croussev</t>
+  </si>
+  <si>
+    <t>ehetzel</t>
+  </si>
+  <si>
+    <t>fcasatilewandowski</t>
+  </si>
+  <si>
+    <t>fmoisseron</t>
+  </si>
+  <si>
+    <t>gvandenbroucque</t>
+  </si>
+  <si>
+    <t>jbarretfontealba</t>
+  </si>
+  <si>
+    <t>lbischoff1</t>
+  </si>
+  <si>
+    <t>mangot</t>
+  </si>
+  <si>
+    <t>nrossinidefrancois</t>
+  </si>
+  <si>
+    <t>probilliard</t>
+  </si>
+  <si>
+    <t>rharada</t>
+  </si>
+  <si>
+    <t>slaquayeudine</t>
+  </si>
+  <si>
+    <t>taubry1</t>
+  </si>
+  <si>
+    <t>tprechal</t>
+  </si>
+  <si>
+    <t>adorlandepolignac</t>
+  </si>
+  <si>
+    <t>aeorthmannreichenbach</t>
+  </si>
+  <si>
+    <t>arauline</t>
+  </si>
+  <si>
+    <t>eleroux</t>
+  </si>
+  <si>
+    <t>ezemihi</t>
+  </si>
+  <si>
+    <t>fcantau</t>
+  </si>
+  <si>
+    <t>fcusmir</t>
+  </si>
+  <si>
+    <t>gbaltardive</t>
+  </si>
+  <si>
+    <t>ggabel</t>
+  </si>
+  <si>
+    <t>hhernout</t>
+  </si>
+  <si>
+    <t>ivalem</t>
+  </si>
+  <si>
+    <t>knajerahoubiers</t>
+  </si>
+  <si>
+    <t>llelayjardin</t>
+  </si>
+  <si>
+    <t>mbianchi</t>
+  </si>
+  <si>
+    <t>nkittel</t>
+  </si>
+  <si>
+    <t>nlancelotmahe</t>
+  </si>
+  <si>
+    <t>sperarnaudaramendi</t>
+  </si>
+  <si>
+    <t>vamirtahmasseb</t>
+  </si>
+  <si>
+    <t>vharnois</t>
+  </si>
+  <si>
+    <t>ygomi</t>
+  </si>
+  <si>
+    <t>yli2</t>
+  </si>
+  <si>
+    <t>aguyduche</t>
+  </si>
+  <si>
+    <t>anantois</t>
+  </si>
+  <si>
+    <t>croszak</t>
+  </si>
+  <si>
+    <t>lchavanon</t>
+  </si>
+  <si>
+    <t>lexbrayat</t>
+  </si>
+  <si>
+    <t>lloube</t>
+  </si>
+  <si>
+    <t>lxiao</t>
+  </si>
+  <si>
+    <t>mmarchessaury</t>
+  </si>
+  <si>
+    <t>nmetivierragonnet</t>
+  </si>
+  <si>
+    <t>odesousapires</t>
+  </si>
+  <si>
+    <t>rleleu1</t>
+  </si>
+  <si>
+    <t>sarchimbaudadad</t>
+  </si>
+  <si>
+    <t>shamdoun</t>
+  </si>
+  <si>
+    <t>erall</t>
+  </si>
+  <si>
+    <t>erebuschi</t>
+  </si>
+  <si>
+    <t>gdelattre</t>
+  </si>
+  <si>
+    <t>jdu</t>
+  </si>
+  <si>
+    <t>mkim</t>
+  </si>
+  <si>
+    <t>mplassard1</t>
+  </si>
+  <si>
+    <t>rcohenakenine</t>
+  </si>
+  <si>
+    <t>rsaillefebvre</t>
+  </si>
+  <si>
+    <t>sleblanclarosa</t>
+  </si>
+  <si>
+    <t>vesnault</t>
+  </si>
+  <si>
+    <t>adecaens</t>
+  </si>
+  <si>
+    <t>amoreira1</t>
+  </si>
+  <si>
+    <t>apichard</t>
+  </si>
+  <si>
+    <t>dwang</t>
+  </si>
+  <si>
+    <t>rgrevin</t>
+  </si>
+  <si>
+    <t>zlyu</t>
+  </si>
+  <si>
+    <t>mlauriac</t>
+  </si>
+  <si>
+    <t>mpascal1</t>
+  </si>
+  <si>
+    <t>cvallapesendorfer</t>
+  </si>
+  <si>
+    <t>scohen</t>
+  </si>
+  <si>
+    <t>ogonzalezbabiaud</t>
+  </si>
+  <si>
+    <t>003482</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>test B</t>
+  </si>
+  <si>
+    <t>fdlsmkfds</t>
+  </si>
+  <si>
+    <t>lmklmdsklmfd</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -70,8 +830,40 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFAAAAAA"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -81,6 +873,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1011A"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEEEEE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF0D8"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EDF7"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -93,17 +909,38 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Neutre" xfId="1" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{2F136823-DD12-4D55-A696-E26F5BADA2AB}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -119,9 +956,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -159,7 +996,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -265,7 +1102,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -407,7 +1244,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -415,24 +1252,1745 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE1BF303-48A1-48AE-BCBD-D3F9B41FFC0F}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.5546875" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>254</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>254</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>254</v>
+      </c>
+      <c r="D6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>254</v>
+      </c>
+      <c r="D7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>254</v>
+      </c>
+      <c r="D8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>254</v>
+      </c>
+      <c r="D9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
+        <v>254</v>
+      </c>
+      <c r="D10" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
+        <v>254</v>
+      </c>
+      <c r="D11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>254</v>
+      </c>
+      <c r="D12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" t="s">
+        <v>254</v>
+      </c>
+      <c r="D13" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" t="s">
+        <v>254</v>
+      </c>
+      <c r="D14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D15" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" t="s">
+        <v>254</v>
+      </c>
+      <c r="D16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
+        <v>254</v>
+      </c>
+      <c r="D17" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" t="s">
+        <v>254</v>
+      </c>
+      <c r="D18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
+        <v>254</v>
+      </c>
+      <c r="D19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" t="s">
+        <v>254</v>
+      </c>
+      <c r="D20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" t="s">
+        <v>254</v>
+      </c>
+      <c r="D21" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" t="s">
+        <v>254</v>
+      </c>
+      <c r="D22" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" t="s">
+        <v>254</v>
+      </c>
+      <c r="D23" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" t="s">
+        <v>254</v>
+      </c>
+      <c r="D24" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" t="s">
+        <v>254</v>
+      </c>
+      <c r="D25" t="s">
+        <v>5</v>
+      </c>
+      <c r="E25" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" t="s">
+        <v>254</v>
+      </c>
+      <c r="D26" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" t="s">
+        <v>254</v>
+      </c>
+      <c r="D27" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" t="s">
+        <v>254</v>
+      </c>
+      <c r="D28" t="s">
+        <v>5</v>
+      </c>
+      <c r="E28" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" t="s">
+        <v>254</v>
+      </c>
+      <c r="D29" t="s">
+        <v>5</v>
+      </c>
+      <c r="E29" t="s">
+        <v>256</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F57133-6941-4E9B-B6C7-45CB54F799A2}">
+  <dimension ref="A1:A246"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A63" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A64" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" s="10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A75" s="8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A76" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A77" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A78" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A79" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A80" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" s="10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A82" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A83" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A86" s="9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A87" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A88" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A89" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A90" s="10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A91" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A92" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A93" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A94" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A95" s="10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A96" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A97" s="10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A98" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A99" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A100" s="10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A101" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A102" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A103" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A104" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A105" s="10" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A106" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A107" s="8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A108" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A109" s="8" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A110" s="7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A111" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A112" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A113" s="10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A114" s="7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A115" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A116" s="7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A117" s="8" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A118" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A119" s="8" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A120" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A121" s="10" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A122" s="10" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A123" s="8" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A124" s="7" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A125" s="8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A126" s="7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A127" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A128" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A129" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A130" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A131" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A132" s="7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A133" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A134" s="10" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A135" s="8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A136" s="10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A137" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A138" s="10" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A139" s="8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A140" s="7" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A141" s="8" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A142" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A143" s="10" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A144" s="7" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A145" s="8" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A146" s="7" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A147" s="10" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A148" s="10" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A149" s="10" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A150" s="10" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A151" s="10" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A152" s="7" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A153" s="8" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A154" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A155" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A156" s="7" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A157" s="8" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A158" s="7" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A159" s="8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A160" s="10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A161" s="8" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A162" s="7" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A163" s="8" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A164" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A165" s="8" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A166" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A167" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A168" s="10" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A169" s="8" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A170" s="10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A171" s="8" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A172" s="7" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A173" s="8" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A174" s="7" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A175" s="8" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A176" s="7" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A177" s="8" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A178" s="7" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A179" s="8" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A180" s="7" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A181" s="8" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A182" s="7" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A183" s="8" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A184" s="7" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A185" s="8" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A186" s="7" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A187" s="8" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A188" s="7" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A189" s="8" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A190" s="7" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A191" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A192" s="7" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A193" s="8" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A194" s="7" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A195" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A196" s="10" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A197" s="8" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A198" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A199" s="10" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A200" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A201" s="8" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A202" s="7" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A203" s="8" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A204" s="7" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A205" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A206" s="7" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A207" s="8" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A208" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A209" s="8" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A210" s="7" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A211" s="8" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A212" s="7" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A213" s="8" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A214" s="10" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A215" s="8" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A216" s="7" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A217" s="10" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A218" s="7" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A219" s="10" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A220" s="7" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A221" s="8" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A222" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A223" s="8" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A224" s="7" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A225" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A226" s="7" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A227" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A228" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A229" s="10" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A230" s="7" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A231" s="8" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A232" s="7" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A233" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A234" s="7" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A235" s="8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A236" s="7" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A237" s="8" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A238" s="7" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A239" s="8" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A240" s="7" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A241" s="8" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A242" s="7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A243" s="8" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A244" s="7" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A245" s="10" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A246" s="7" t="s">
+        <v>252</v>
       </c>
     </row>
   </sheetData>

--- a/evaluations.xlsx
+++ b/evaluations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hhoar\IdeaProjects\OasisTools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA4A0AC-90F8-4D97-936E-4BB795AB219B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE9394BF-EA8C-410E-A677-C6CA59AADE47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="11370" windowWidth="29040" windowHeight="15720" xr2:uid="{7A85ACFF-515C-4F42-BD6C-13C15AB38619}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="34776" windowHeight="18936" xr2:uid="{7A85ACFF-515C-4F42-BD6C-13C15AB38619}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -796,9 +796,6 @@
     <t>ogonzalezbabiaud</t>
   </si>
   <si>
-    <t>003482</t>
-  </si>
-  <si>
     <t>B</t>
   </si>
   <si>
@@ -809,6 +806,9 @@
   </si>
   <si>
     <t>lmklmdsklmfd</t>
+  </si>
+  <si>
+    <t>003481</t>
   </si>
 </sst>
 </file>
@@ -956,9 +956,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -996,7 +996,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1102,7 +1102,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1244,7 +1244,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1277,7 +1277,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>7</v>
@@ -1289,466 +1289,466 @@
         <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D5" t="s">
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D7" t="s">
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D8" t="s">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D9" t="s">
         <v>5</v>
       </c>
       <c r="E9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D10" t="s">
         <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D11" t="s">
         <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D12" t="s">
         <v>5</v>
       </c>
       <c r="E12" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D13" t="s">
         <v>5</v>
       </c>
       <c r="E13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D14" t="s">
         <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D15" t="s">
         <v>5</v>
       </c>
       <c r="E15" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
       </c>
       <c r="E16" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D17" t="s">
         <v>5</v>
       </c>
       <c r="E17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D18" t="s">
         <v>5</v>
       </c>
       <c r="E18" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D19" t="s">
         <v>5</v>
       </c>
       <c r="E19" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D20" t="s">
         <v>5</v>
       </c>
       <c r="E20" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>28</v>
       </c>
       <c r="C21" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D21" t="s">
         <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>29</v>
       </c>
       <c r="C22" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D22" t="s">
         <v>5</v>
       </c>
       <c r="E22" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>30</v>
       </c>
       <c r="C23" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D23" t="s">
         <v>5</v>
       </c>
       <c r="E23" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>31</v>
       </c>
       <c r="C24" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D24" t="s">
         <v>5</v>
       </c>
       <c r="E24" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>32</v>
       </c>
       <c r="C25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D25" t="s">
         <v>5</v>
       </c>
       <c r="E25" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>33</v>
       </c>
       <c r="C26" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D26" t="s">
         <v>5</v>
       </c>
       <c r="E26" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>34</v>
       </c>
       <c r="C27" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D27" t="s">
         <v>5</v>
       </c>
       <c r="E27" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>35</v>
       </c>
       <c r="C28" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D28" t="s">
         <v>5</v>
       </c>
       <c r="E28" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>36</v>
       </c>
       <c r="C29" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D29" t="s">
         <v>5</v>
       </c>
       <c r="E29" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>
